--- a/game/data/game_config.xlsx
+++ b/game/data/game_config.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="使用说明" sheetId="1" r:id="R15dbab3584914843"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="对话" sheetId="2" r:id="Rf4dbd024d322463a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="图片资源" sheetId="3" r:id="R34c7f9dc8ff244f7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI" sheetId="4" r:id="Rc3e9e8734fcb492e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="使用说明" sheetId="1" r:id="R9f5af00b8c834c7a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="对话" sheetId="2" r:id="Rd967ed56d2b54023"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="图片资源" sheetId="3" r:id="Rc7df99987db04c34"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI" sheetId="4" r:id="Rfa5dd6c6dd6348c9"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -15466,16 +15466,16 @@
         <x:v>squad_frame</x:v>
       </x:c>
       <x:c r="B29" s="20" t="n">
-        <x:v>72</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C29" s="20" t="n">
-        <x:v>42</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D29" s="20" t="n">
-        <x:v>1136</x:v>
+        <x:v>1184</x:v>
       </x:c>
       <x:c r="E29" s="20" t="n">
-        <x:v>636</x:v>
+        <x:v>672</x:v>
       </x:c>
       <x:c r="F29" s="19" t="str"/>
       <x:c r="G29" s="19" t="str">
@@ -15509,16 +15509,16 @@
         <x:v>squad_title</x:v>
       </x:c>
       <x:c r="B30" s="20" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C30" s="20" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="D30" s="20" t="n">
+        <x:v>720</x:v>
+      </x:c>
+      <x:c r="E30" s="20" t="n">
         <x:v>36</x:v>
-      </x:c>
-      <x:c r="C30" s="20" t="n">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="D30" s="20" t="n">
-        <x:v>700</x:v>
-      </x:c>
-      <x:c r="E30" s="20" t="n">
-        <x:v>42</x:v>
       </x:c>
       <x:c r="F30" s="19" t="str"/>
       <x:c r="G30" s="19" t="str">
@@ -15552,16 +15552,16 @@
         <x:v>squad_subtitle</x:v>
       </x:c>
       <x:c r="B31" s="20" t="n">
-        <x:v>36</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C31" s="20" t="n">
-        <x:v>94</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="D31" s="20" t="n">
         <x:v>900</x:v>
       </x:c>
       <x:c r="E31" s="20" t="n">
-        <x:v>24</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F31" s="19" t="str"/>
       <x:c r="G31" s="19" t="str">
@@ -15595,16 +15595,16 @@
         <x:v>squad_confirm</x:v>
       </x:c>
       <x:c r="B32" s="20" t="n">
-        <x:v>308</x:v>
+        <x:v>324</x:v>
       </x:c>
       <x:c r="C32" s="20" t="n">
-        <x:v>500</x:v>
+        <x:v>548</x:v>
       </x:c>
       <x:c r="D32" s="20" t="n">
-        <x:v>520</x:v>
+        <x:v>536</x:v>
       </x:c>
       <x:c r="E32" s="20" t="n">
-        <x:v>54</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="F32" s="19" t="str"/>
       <x:c r="G32" s="19" t="str">
@@ -15640,16 +15640,16 @@
         <x:v>squad_character_1</x:v>
       </x:c>
       <x:c r="B33" s="20" t="n">
-        <x:v>36</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C33" s="20" t="n">
-        <x:v>142</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="D33" s="20" t="n">
-        <x:v>250</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="E33" s="20" t="n">
-        <x:v>132</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="F33" s="19" t="str"/>
       <x:c r="G33" s="19" t="str">
@@ -15683,16 +15683,16 @@
         <x:v>squad_character_2</x:v>
       </x:c>
       <x:c r="B34" s="20" t="n">
-        <x:v>304</x:v>
+        <x:v>315</x:v>
       </x:c>
       <x:c r="C34" s="20" t="n">
-        <x:v>142</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="D34" s="20" t="n">
-        <x:v>250</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="E34" s="20" t="n">
-        <x:v>132</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="F34" s="19" t="str"/>
       <x:c r="G34" s="19" t="str">
@@ -15726,16 +15726,16 @@
         <x:v>squad_character_3</x:v>
       </x:c>
       <x:c r="B35" s="20" t="n">
-        <x:v>572</x:v>
+        <x:v>600</x:v>
       </x:c>
       <x:c r="C35" s="20" t="n">
-        <x:v>142</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="D35" s="20" t="n">
-        <x:v>250</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="E35" s="20" t="n">
-        <x:v>132</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="F35" s="19" t="str"/>
       <x:c r="G35" s="19" t="str">
@@ -15769,16 +15769,16 @@
         <x:v>squad_character_4</x:v>
       </x:c>
       <x:c r="B36" s="20" t="n">
-        <x:v>840</x:v>
+        <x:v>885</x:v>
       </x:c>
       <x:c r="C36" s="20" t="n">
-        <x:v>142</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="D36" s="20" t="n">
-        <x:v>250</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="E36" s="20" t="n">
-        <x:v>132</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="F36" s="19" t="str"/>
       <x:c r="G36" s="19" t="str">
@@ -15812,16 +15812,16 @@
         <x:v>squad_character_5</x:v>
       </x:c>
       <x:c r="B37" s="20" t="n">
-        <x:v>36</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C37" s="20" t="n">
-        <x:v>298</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="D37" s="20" t="n">
-        <x:v>250</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="E37" s="20" t="n">
-        <x:v>132</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="F37" s="19" t="str"/>
       <x:c r="G37" s="19" t="str">
@@ -15855,16 +15855,16 @@
         <x:v>squad_character_6</x:v>
       </x:c>
       <x:c r="B38" s="20" t="n">
-        <x:v>304</x:v>
+        <x:v>315</x:v>
       </x:c>
       <x:c r="C38" s="20" t="n">
-        <x:v>298</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="D38" s="20" t="n">
-        <x:v>250</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="E38" s="20" t="n">
-        <x:v>132</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="F38" s="19" t="str"/>
       <x:c r="G38" s="19" t="str">
@@ -15898,16 +15898,16 @@
         <x:v>squad_character_7</x:v>
       </x:c>
       <x:c r="B39" s="20" t="n">
-        <x:v>572</x:v>
+        <x:v>600</x:v>
       </x:c>
       <x:c r="C39" s="20" t="n">
-        <x:v>298</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="D39" s="20" t="n">
-        <x:v>250</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="E39" s="20" t="n">
-        <x:v>132</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="F39" s="19" t="str"/>
       <x:c r="G39" s="19" t="str">
@@ -15941,16 +15941,16 @@
         <x:v>squad_character_8</x:v>
       </x:c>
       <x:c r="B40" s="20" t="n">
-        <x:v>840</x:v>
+        <x:v>885</x:v>
       </x:c>
       <x:c r="C40" s="20" t="n">
-        <x:v>298</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="D40" s="20" t="n">
-        <x:v>250</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="E40" s="20" t="n">
-        <x:v>132</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="F40" s="19" t="str"/>
       <x:c r="G40" s="19" t="str">
@@ -16240,72 +16240,176 @@
       </x:c>
     </x:row>
     <x:row r="47" ht="30" customHeight="1">
-      <x:c r="A47" s="12"/>
-      <x:c r="B47" s="14"/>
-      <x:c r="C47" s="14"/>
-      <x:c r="D47" s="14"/>
-      <x:c r="E47" s="14"/>
-      <x:c r="F47" s="12"/>
-      <x:c r="G47" s="12"/>
-      <x:c r="H47" s="13"/>
-      <x:c r="I47" s="14"/>
-      <x:c r="J47" s="14"/>
-      <x:c r="K47" s="14"/>
-      <x:c r="L47" s="14"/>
-      <x:c r="M47" s="14"/>
-      <x:c r="N47" s="13"/>
-      <x:c r="O47" s="14"/>
+      <x:c r="A47" s="12" t="str">
+        <x:v>squad_character_9</x:v>
+      </x:c>
+      <x:c r="B47" s="14" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C47" s="14" t="n">
+        <x:v>392</x:v>
+      </x:c>
+      <x:c r="D47" s="14" t="n">
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="E47" s="14" t="n">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="F47" s="12" t="str"/>
+      <x:c r="G47" s="12" t="str">
+        <x:v>stretch</x:v>
+      </x:c>
+      <x:c r="H47" s="13" t="str"/>
+      <x:c r="I47" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J47" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K47" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L47" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M47" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N47" s="13" t="str">
+        <x:v>角色槽位 9</x:v>
+      </x:c>
+      <x:c r="O47" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="48" ht="30" customHeight="1">
-      <x:c r="A48" s="12"/>
-      <x:c r="B48" s="14"/>
-      <x:c r="C48" s="14"/>
-      <x:c r="D48" s="14"/>
-      <x:c r="E48" s="14"/>
-      <x:c r="F48" s="12"/>
-      <x:c r="G48" s="12"/>
-      <x:c r="H48" s="13"/>
-      <x:c r="I48" s="14"/>
-      <x:c r="J48" s="14"/>
-      <x:c r="K48" s="14"/>
-      <x:c r="L48" s="14"/>
-      <x:c r="M48" s="14"/>
-      <x:c r="N48" s="13"/>
-      <x:c r="O48" s="14"/>
+      <x:c r="A48" s="12" t="str">
+        <x:v>squad_character_10</x:v>
+      </x:c>
+      <x:c r="B48" s="14" t="n">
+        <x:v>315</x:v>
+      </x:c>
+      <x:c r="C48" s="14" t="n">
+        <x:v>392</x:v>
+      </x:c>
+      <x:c r="D48" s="14" t="n">
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="E48" s="14" t="n">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="F48" s="12" t="str"/>
+      <x:c r="G48" s="12" t="str">
+        <x:v>stretch</x:v>
+      </x:c>
+      <x:c r="H48" s="13" t="str"/>
+      <x:c r="I48" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J48" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K48" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L48" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M48" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N48" s="13" t="str">
+        <x:v>角色槽位 10</x:v>
+      </x:c>
+      <x:c r="O48" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="49" ht="30" customHeight="1">
-      <x:c r="A49" s="12"/>
-      <x:c r="B49" s="14"/>
-      <x:c r="C49" s="14"/>
-      <x:c r="D49" s="14"/>
-      <x:c r="E49" s="14"/>
-      <x:c r="F49" s="12"/>
-      <x:c r="G49" s="12"/>
-      <x:c r="H49" s="13"/>
-      <x:c r="I49" s="14"/>
-      <x:c r="J49" s="14"/>
-      <x:c r="K49" s="14"/>
-      <x:c r="L49" s="14"/>
-      <x:c r="M49" s="14"/>
-      <x:c r="N49" s="13"/>
-      <x:c r="O49" s="14"/>
+      <x:c r="A49" s="12" t="str">
+        <x:v>squad_character_11</x:v>
+      </x:c>
+      <x:c r="B49" s="14" t="n">
+        <x:v>600</x:v>
+      </x:c>
+      <x:c r="C49" s="14" t="n">
+        <x:v>392</x:v>
+      </x:c>
+      <x:c r="D49" s="14" t="n">
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="E49" s="14" t="n">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="F49" s="12" t="str"/>
+      <x:c r="G49" s="12" t="str">
+        <x:v>stretch</x:v>
+      </x:c>
+      <x:c r="H49" s="13" t="str"/>
+      <x:c r="I49" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J49" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K49" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L49" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M49" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N49" s="13" t="str">
+        <x:v>角色槽位 11</x:v>
+      </x:c>
+      <x:c r="O49" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="50" ht="30" customHeight="1">
-      <x:c r="A50" s="12"/>
-      <x:c r="B50" s="14"/>
-      <x:c r="C50" s="14"/>
-      <x:c r="D50" s="14"/>
-      <x:c r="E50" s="14"/>
-      <x:c r="F50" s="12"/>
-      <x:c r="G50" s="12"/>
-      <x:c r="H50" s="13"/>
-      <x:c r="I50" s="14"/>
-      <x:c r="J50" s="14"/>
-      <x:c r="K50" s="14"/>
-      <x:c r="L50" s="14"/>
-      <x:c r="M50" s="14"/>
-      <x:c r="N50" s="13"/>
-      <x:c r="O50" s="14"/>
+      <x:c r="A50" s="12" t="str">
+        <x:v>squad_character_12</x:v>
+      </x:c>
+      <x:c r="B50" s="14" t="n">
+        <x:v>885</x:v>
+      </x:c>
+      <x:c r="C50" s="14" t="n">
+        <x:v>392</x:v>
+      </x:c>
+      <x:c r="D50" s="14" t="n">
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="E50" s="14" t="n">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="F50" s="12" t="str"/>
+      <x:c r="G50" s="12" t="str">
+        <x:v>stretch</x:v>
+      </x:c>
+      <x:c r="H50" s="13" t="str"/>
+      <x:c r="I50" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J50" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K50" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L50" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M50" s="14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N50" s="13" t="str">
+        <x:v>角色槽位 12</x:v>
+      </x:c>
+      <x:c r="O50" s="14" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="51" ht="30" customHeight="1">
       <x:c r="A51" s="12"/>
